--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>136349435</v>
       </c>
       <c r="B8" t="n">
-        <v>56976</v>
+        <v>56978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136349431</v>
       </c>
       <c r="B23" t="n">
-        <v>58281</v>
+        <v>58283</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
